--- a/Python-Based Projects/HR-Data-Cleaning-Project/data/HR_Cleaned_Data.xlsx
+++ b/Python-Based Projects/HR-Data-Cleaning-Project/data/HR_Cleaned_Data.xlsx
@@ -10063,7 +10063,7 @@
         <v>39972</v>
       </c>
       <c r="G114" t="n">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>38261</v>
       </c>
       <c r="G137" t="n">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>41548</v>
       </c>
       <c r="G303" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>42198</v>
       </c>
       <c r="G324" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Operatons</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E342" t="n">
@@ -31629,7 +31629,7 @@
         <v>42089</v>
       </c>
       <c r="G368" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H368" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Operatons</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E427" t="n">
@@ -39949,7 +39949,7 @@
         <v>38599</v>
       </c>
       <c r="G466" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H466" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
       </c>
       <c r="F496" t="inlineStr"/>
       <c r="G496" t="n">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="H496" t="inlineStr">
         <is>
@@ -47413,7 +47413,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>Operatons</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E554" t="n">
@@ -48781,7 +48781,7 @@
       </c>
       <c r="F570" t="inlineStr"/>
       <c r="G570" t="n">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="H570" t="inlineStr">
         <is>
@@ -51319,7 +51319,7 @@
         <v>37248</v>
       </c>
       <c r="G600" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H600" t="inlineStr">
         <is>
@@ -56237,7 +56237,7 @@
         <v>43160</v>
       </c>
       <c r="G658" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H658" t="inlineStr">
         <is>
@@ -57413,7 +57413,7 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Operatons</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E672" t="n">
@@ -58781,7 +58781,7 @@
         <v>42474</v>
       </c>
       <c r="G688" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H688" t="inlineStr">
         <is>
@@ -59714,7 +59714,7 @@
         <v>39629</v>
       </c>
       <c r="G699" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H699" t="inlineStr">
         <is>
@@ -67419,7 +67419,7 @@
         <v>39535</v>
       </c>
       <c r="G790" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H790" t="inlineStr">
         <is>
@@ -68775,7 +68775,7 @@
         <v>40151</v>
       </c>
       <c r="G806" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H806" t="inlineStr">
         <is>
@@ -70036,7 +70036,7 @@
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>Operatons</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E821" t="n">
@@ -70457,7 +70457,7 @@
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>Operatons</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E826" t="n">
@@ -73013,7 +73013,7 @@
         <v>40643</v>
       </c>
       <c r="G856" t="n">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="H856" t="inlineStr">
         <is>
@@ -73513,7 +73513,7 @@
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>Operatons</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="E862" t="n">
